--- a/src/attributions/attributions_ig_traj_263.xlsx
+++ b/src/attributions/attributions_ig_traj_263.xlsx
@@ -1571,34 +1571,34 @@
         <v>-0</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.5907423720510372</v>
+        <v>-0.2637164065598414</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
         <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04859924474472172</v>
+        <v>-0.04095303811763519</v>
       </c>
       <c r="F3" t="n">
-        <v>0.711747493782801</v>
+        <v>0.1846994799202987</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.3014753978027011</v>
+        <v>-0.1782377556311488</v>
       </c>
       <c r="L3" t="n">
         <v>-0</v>
@@ -1607,25 +1607,25 @@
         <v>-0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.09100367872707554</v>
+        <v>0.0452095607196455</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4218455683183934</v>
+        <v>0.138012119890587</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1283241928056585</v>
+        <v>-0.1414519628617855</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1634,16 +1634,16 @@
         <v>-0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2320070138984469</v>
+        <v>0.01884081756956921</v>
       </c>
       <c r="X3" t="n">
-        <v>0.04697145441791028</v>
+        <v>0.02835455527419715</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>-0</v>
@@ -1652,19 +1652,19 @@
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.03716571468091258</v>
+        <v>0.1804714992812778</v>
       </c>
       <c r="AD3" t="n">
         <v>-0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.07571911925585616</v>
+        <v>0.1418311026788206</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.08617762957233899</v>
+        <v>0.03898917896299974</v>
       </c>
       <c r="AH3" t="n">
         <v>-0</v>
@@ -1676,22 +1676,22 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.05356383414778983</v>
+        <v>-0.1389299701962969</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.05086420014854205</v>
+        <v>-0.1420863398166642</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.283635253779179</v>
+        <v>0.13299137659035</v>
       </c>
       <c r="AQ3" t="n">
         <v>0</v>
@@ -1703,22 +1703,22 @@
         <v>-0</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.6545726300252076</v>
+        <v>-0.6680072668787855</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.353742286798557</v>
+        <v>-0.02014908367058205</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.7967218061298216</v>
+        <v>0.1705225535380095</v>
       </c>
       <c r="AZ3" t="n">
         <v>-0</v>
@@ -1727,13 +1727,13 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.2590685823349752</v>
+        <v>0.3012875686204984</v>
       </c>
       <c r="BE3" t="n">
         <v>-0</v>
@@ -1742,37 +1742,37 @@
         <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.03999448990986509</v>
+        <v>0.2126155546216148</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.07365716320560284</v>
+        <v>0.05693073514055617</v>
       </c>
       <c r="BI3" t="n">
         <v>-0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.1950987718550657</v>
+        <v>-0.04168225364630181</v>
       </c>
       <c r="BN3" t="n">
         <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.06242148498241985</v>
+        <v>-0.01177232678557138</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-0.0370323116097788</v>
+        <v>-0.05019266683159581</v>
       </c>
       <c r="BR3" t="n">
         <v>-0</v>
@@ -1787,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.387306059861792</v>
+        <v>-0.4119586126204284</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
@@ -1796,16 +1796,16 @@
         <v>-0</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.1049089077551393</v>
+        <v>-0.03604316816120488</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.3547369034953312</v>
+        <v>0.1703864207687728</v>
       </c>
       <c r="CA3" t="n">
         <v>0</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC3" t="n">
         <v>0</v>
@@ -1814,46 +1814,46 @@
         <v>0</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.2173391283594683</v>
+        <v>0.2042103681989101</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG3" t="n">
         <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.05077110125879324</v>
+        <v>0.0009876376973725399</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.2160686874341345</v>
+        <v>-0.0790527493180059</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK3" t="n">
         <v>-0</v>
       </c>
       <c r="CL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM3" t="n">
         <v>-0</v>
       </c>
       <c r="CN3" t="n">
-        <v>-0.00611151429239101</v>
+        <v>0.05997956585670863</v>
       </c>
       <c r="CO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.02343643489932451</v>
+        <v>-0.0481589034243897</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.07523881062452112</v>
+        <v>-0.01943684051614997</v>
       </c>
       <c r="CS3" t="n">
         <v>0</v>
@@ -1868,19 +1868,19 @@
         <v>0</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.2113661264768439</v>
+        <v>0.20338587736906</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY3" t="n">
         <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.01616342693238502</v>
+        <v>0.003134953258286974</v>
       </c>
       <c r="DA3" t="n">
-        <v>-0.2359284008468303</v>
+        <v>-0.08570551677012292</v>
       </c>
       <c r="DB3" t="n">
         <v>-0</v>
@@ -1895,19 +1895,19 @@
         <v>-0</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.2885312849019981</v>
+        <v>0.1883563737488653</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH3" t="n">
         <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.4245215522540731</v>
+        <v>0.06125918884186034</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.02626962581259099</v>
+        <v>-0.03100115126574298</v>
       </c>
       <c r="DK3" t="n">
         <v>-0</v>
@@ -1916,25 +1916,25 @@
         <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.13773514152246</v>
+        <v>-0.00206263470103419</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ3" t="n">
         <v>-0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0.02616147785458756</v>
+        <v>0.06844316780605066</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.004402933469357772</v>
+        <v>-0.1301786396375339</v>
       </c>
       <c r="DT3" t="n">
         <v>0</v>
@@ -1943,13 +1943,13 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.1256688917354761</v>
+        <v>0.1490512565015825</v>
       </c>
       <c r="DY3" t="n">
         <v>0</v>
@@ -1958,79 +1958,79 @@
         <v>0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.1057251023150817</v>
+        <v>-0.07146542140486702</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.1252414853679507</v>
+        <v>-0.03908852515362736</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED3" t="n">
         <v>-0</v>
       </c>
       <c r="EE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF3" t="n">
         <v>-0</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.1546543477832351</v>
+        <v>0.08967739948300296</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.009975466117810555</v>
+        <v>0.03686136171398743</v>
       </c>
       <c r="EK3" t="n">
-        <v>-0.1969047244918906</v>
+        <v>0.07619399622577186</v>
       </c>
       <c r="EL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM3" t="n">
         <v>0</v>
       </c>
       <c r="EN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.1143800627807219</v>
+        <v>0.1122487971985849</v>
       </c>
       <c r="EQ3" t="n">
         <v>0</v>
       </c>
       <c r="ER3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.04000046568875275</v>
+        <v>0.1015330100144615</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.08710789296033682</v>
+        <v>0.03147009063814944</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX3" t="n">
         <v>-0</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.1973086141780908</v>
+        <v>0.2333995844781776</v>
       </c>
       <c r="EZ3" t="n">
         <v>0</v>
@@ -2039,52 +2039,52 @@
         <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.03569389340623406</v>
+        <v>0.01933192060229198</v>
       </c>
       <c r="FC3" t="n">
-        <v>-0.2221494924589265</v>
+        <v>-0.08185006471590738</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF3" t="n">
         <v>0</v>
       </c>
       <c r="FG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0.06329281130798373</v>
+        <v>-0.223698953308134</v>
       </c>
       <c r="FI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ3" t="n">
         <v>0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.05288449340779308</v>
+        <v>0.06443219327716332</v>
       </c>
       <c r="FL3" t="n">
-        <v>-0.1332843252969251</v>
+        <v>-0.1230976927818782</v>
       </c>
       <c r="FM3" t="n">
         <v>-0</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.160100848963802</v>
+        <v>0.3565004125516593</v>
       </c>
       <c r="FR3" t="n">
         <v>0</v>
@@ -2093,13 +2093,13 @@
         <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.1478336404981344</v>
+        <v>-0.0803928320744859</v>
       </c>
       <c r="FU3" t="n">
-        <v>-0.168392163565188</v>
+        <v>-0.05986305778447953</v>
       </c>
       <c r="FV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW3" t="n">
         <v>0</v>
@@ -2108,22 +2108,22 @@
         <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.0001889799112203393</v>
+        <v>0.1919945941592312</v>
       </c>
       <c r="GA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB3" t="n">
         <v>0</v>
       </c>
       <c r="GC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.1332478748040545</v>
+        <v>-0.03734341910180818</v>
       </c>
       <c r="GE3" t="n">
         <v>0</v>
@@ -2132,84 +2132,84 @@
         <v>-0</v>
       </c>
       <c r="GG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.1521772830035362</v>
+        <v>-0.07754985353522997</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01215103800995104</v>
+        <v>0.005729895338412413</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4350182245248214</v>
+        <v>0.1698801553850012</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0568742348184748</v>
+        <v>-0.05053631322324134</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>-0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.01445901810721536</v>
+        <v>0.05528113874347287</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3576509212326078</v>
+        <v>0.1753967785611765</v>
       </c>
       <c r="P4" t="n">
         <v>-0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01282626050752159</v>
+        <v>-0.09670256828405088</v>
       </c>
       <c r="U4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.04499269138105853</v>
+        <v>0.02763868224569845</v>
       </c>
       <c r="X4" t="n">
-        <v>0.06760449213046153</v>
+        <v>0.05232352153985046</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -2221,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.1169774147137127</v>
+        <v>0.0120273619333074</v>
       </c>
       <c r="AD4" t="n">
         <v>-0</v>
@@ -2230,40 +2230,40 @@
         <v>-0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.002764354193378348</v>
+        <v>0.09965854324685831</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.03702344420063914</v>
+        <v>0.08271346687953766</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.04657575942929318</v>
+        <v>-0.05603711985529863</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.1540683268576207</v>
+        <v>-0.1033130689762308</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.1734430446350088</v>
+        <v>0.1303729331004448</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2275,34 +2275,34 @@
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.254675532715481</v>
+        <v>-0.3726311916641691</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.08308506772121355</v>
+        <v>-0.1232063157958398</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.5059181620557628</v>
+        <v>0.3741606311023856</v>
       </c>
       <c r="AZ4" t="n">
         <v>-0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
         <v>-0</v>
       </c>
       <c r="BC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.1273780222131285</v>
+        <v>0.1505862014514351</v>
       </c>
       <c r="BE4" t="n">
         <v>-0</v>
@@ -2311,10 +2311,10 @@
         <v>-0</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.07601226739399886</v>
+        <v>0.1834761980237204</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.0882581919784748</v>
+        <v>-0.02929485385872991</v>
       </c>
       <c r="BI4" t="n">
         <v>-0</v>
@@ -2323,13 +2323,13 @@
         <v>-0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>-0.1206938668892954</v>
+        <v>-0.02549453698934601</v>
       </c>
       <c r="BN4" t="n">
         <v>0</v>
@@ -2338,37 +2338,37 @@
         <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.04176773173307172</v>
+        <v>-0.07159333789993501</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.04636658617056875</v>
+        <v>0.0101669376115851</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
         <v>-0</v>
       </c>
       <c r="BU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>-0.1065144763915882</v>
+        <v>-0.1812876933456387</v>
       </c>
       <c r="BW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
         <v>-0</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.1039981458718401</v>
+        <v>-0.03557448472895247</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.270209074928717</v>
+        <v>0.2290705787288714</v>
       </c>
       <c r="CA4" t="n">
         <v>0</v>
@@ -2380,37 +2380,37 @@
         <v>-0</v>
       </c>
       <c r="CD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.09396578190640995</v>
+        <v>0.1052268350486755</v>
       </c>
       <c r="CF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.00293907848045431</v>
+        <v>-0.002324285205295036</v>
       </c>
       <c r="CI4" t="n">
-        <v>-0.1077629868396075</v>
+        <v>-0.1053402140466838</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
         <v>-0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.0002397003366506833</v>
+        <v>0.01566712705345525</v>
       </c>
       <c r="CO4" t="n">
         <v>0</v>
@@ -2419,16 +2419,16 @@
         <v>0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.04216459739408339</v>
+        <v>-0.01613715447349209</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.007458094355911236</v>
+        <v>-0.07563221446326673</v>
       </c>
       <c r="CS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU4" t="n">
         <v>0</v>
@@ -2437,88 +2437,88 @@
         <v>0</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.06740079744560176</v>
+        <v>0.1091935941948791</v>
       </c>
       <c r="CX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY4" t="n">
         <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.003132134578663914</v>
+        <v>-0.003031859699273469</v>
       </c>
       <c r="DA4" t="n">
-        <v>-0.1422361811376694</v>
+        <v>-0.1003895273847724</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD4" t="n">
         <v>-0</v>
       </c>
       <c r="DE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.02122577840165335</v>
+        <v>-8.857847122752486e-05</v>
       </c>
       <c r="DG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.004391219698260184</v>
+        <v>0.009327547134133475</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.01184530190938846</v>
+        <v>-0.01388433277548419</v>
       </c>
       <c r="DK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL4" t="n">
         <v>-0</v>
       </c>
       <c r="DM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.01157932548527461</v>
+        <v>0.06260966363903597</v>
       </c>
       <c r="DP4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.01288231608741803</v>
+        <v>-0.02990463605855149</v>
       </c>
       <c r="DS4" t="n">
-        <v>-0.01655816246350265</v>
+        <v>-0.08501510436928854</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV4" t="n">
         <v>-0</v>
       </c>
       <c r="DW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.06630883920647457</v>
+        <v>0.02828931777540756</v>
       </c>
       <c r="DY4" t="n">
         <v>-0</v>
@@ -2527,16 +2527,16 @@
         <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.02834112367487702</v>
+        <v>-0.03791358309664082</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0.05607673728968418</v>
+        <v>-0.04582414030469325</v>
       </c>
       <c r="EC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
         <v>0</v>
@@ -2545,52 +2545,52 @@
         <v>-0</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.04555015356729805</v>
+        <v>0.04588189046174277</v>
       </c>
       <c r="EH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI4" t="n">
         <v>0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.08519230871250633</v>
+        <v>0.01291005233629032</v>
       </c>
       <c r="EK4" t="n">
-        <v>-0.1273537196015069</v>
+        <v>0.005508369215302609</v>
       </c>
       <c r="EL4" t="n">
         <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
         <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.06237810851093607</v>
+        <v>-0.03795079885445988</v>
       </c>
       <c r="EQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER4" t="n">
         <v>0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.01584234814970653</v>
+        <v>-0.08082943357456451</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.06181154580585027</v>
+        <v>-0.01358949955750432</v>
       </c>
       <c r="EU4" t="n">
         <v>-0</v>
       </c>
       <c r="EV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW4" t="n">
         <v>0</v>
@@ -2599,61 +2599,61 @@
         <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.06319080894542903</v>
+        <v>0.1157479348237192</v>
       </c>
       <c r="EZ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA4" t="n">
         <v>0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.007032725745926586</v>
+        <v>0.0164683407837722</v>
       </c>
       <c r="FC4" t="n">
-        <v>-0.113465351429826</v>
+        <v>-0.09989311416499656</v>
       </c>
       <c r="FD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF4" t="n">
         <v>0</v>
       </c>
       <c r="FG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.01171847791587382</v>
+        <v>0.08960148259921467</v>
       </c>
       <c r="FI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ4" t="n">
         <v>0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.01882954132898579</v>
+        <v>0.02345138565175554</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.1352876509441251</v>
+        <v>0.1043704012258244</v>
       </c>
       <c r="FM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN4" t="n">
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
         <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.08430467660109264</v>
+        <v>0.1740833363272463</v>
       </c>
       <c r="FR4" t="n">
         <v>0</v>
@@ -2662,37 +2662,37 @@
         <v>0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.1589342795688251</v>
+        <v>0.009756637175417155</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.03994801402807724</v>
+        <v>0.07535440664879345</v>
       </c>
       <c r="FV4" t="n">
         <v>0</v>
       </c>
       <c r="FW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.008486862586147396</v>
+        <v>0.06250073150704596</v>
       </c>
       <c r="GA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB4" t="n">
         <v>0</v>
       </c>
       <c r="GC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.06040436420415355</v>
+        <v>-0.01676827004186526</v>
       </c>
       <c r="GE4" t="n">
         <v>0</v>
@@ -2701,15 +2701,15 @@
         <v>0</v>
       </c>
       <c r="GG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1589610711727572</v>
+        <v>0.2857746919583649</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -2718,10 +2718,10 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.04337964506746834</v>
+        <v>0.03537007003892471</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.10106543879525</v>
+        <v>-0.2590523462962723</v>
       </c>
       <c r="G5" t="n">
         <v>-0</v>
@@ -2730,13 +2730,13 @@
         <v>-0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1227449045020368</v>
+        <v>0.3236260504814116</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2745,25 +2745,25 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.01494532506676126</v>
+        <v>-0.08046343143976779</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.05593671828055311</v>
+        <v>-0.207119844763047</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02863058078650222</v>
+        <v>0.09855191790272509</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
@@ -2772,37 +2772,37 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.02229832001961994</v>
+        <v>-0.05429537937613115</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0009944783973878963</v>
+        <v>-0.071265480382568</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB5" t="n">
         <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.0003256268392576414</v>
+        <v>-0.06771747375362412</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0005517397164854005</v>
+        <v>-0.19185046540687</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.008504614147312782</v>
+        <v>0.07939889513096077</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -2817,22 +2817,22 @@
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.02538074766034841</v>
+        <v>0.1261075475215516</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.008424205901947788</v>
+        <v>-0.03590321270631883</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.0502531428929397</v>
+        <v>-0.08781443702498574</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
         <v>-0</v>
@@ -2841,37 +2841,37 @@
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.1463275473736579</v>
+        <v>0.536682793244264</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.03509795254325043</v>
+        <v>-0.2479381628747725</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.109345915823353</v>
+        <v>-0.3030646692191742</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.04932863652300052</v>
+        <v>-0.1032356865571286</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -2880,10 +2880,10 @@
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.04623260542257231</v>
+        <v>0.02523571446271596</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.04530551014053272</v>
+        <v>-0.08249852919421692</v>
       </c>
       <c r="BI5" t="n">
         <v>-0</v>
@@ -2892,13 +2892,13 @@
         <v>-0</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.04281810092315083</v>
+        <v>0.09271060381261344</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
@@ -2907,79 +2907,79 @@
         <v>-0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.02105778762007339</v>
+        <v>0.05598051741071496</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.004317474875009573</v>
+        <v>0.06529185197638886</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>0</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU5" t="n">
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.08404362072520531</v>
+        <v>0.2966657176568378</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
         <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.024025163353162</v>
+        <v>-0.06752403124959275</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.03217315708767531</v>
+        <v>-0.1670550283776666</v>
       </c>
       <c r="CA5" t="n">
         <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
         <v>-0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.04130357840418181</v>
+        <v>-0.1482602087757987</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
         <v>-0</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.002236600239076929</v>
+        <v>0.03577410811814859</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.03427002024254591</v>
+        <v>0.09379327247709286</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
         <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM5" t="n">
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>5.835430320860319e-05</v>
+        <v>-0.06479243335494052</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
@@ -2988,37 +2988,37 @@
         <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.0005470976653379152</v>
+        <v>0.07209929022827558</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.008606977068776637</v>
+        <v>-0.003504962134377902</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
         <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.03680334579194405</v>
+        <v>-0.1408385134544604</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
         <v>0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.006678294474540209</v>
+        <v>0.01682759595277486</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.0378188200655074</v>
+        <v>0.1273312971613949</v>
       </c>
       <c r="DB5" t="n">
         <v>0</v>
@@ -3027,25 +3027,25 @@
         <v>-0</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.005967600968891288</v>
+        <v>0.02225370653475057</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.05092798024129717</v>
+        <v>-0.02281476586838516</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.00205764002187583</v>
+        <v>0.04553104920106683</v>
       </c>
       <c r="DK5" t="n">
         <v>0</v>
@@ -3054,13 +3054,13 @@
         <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.01912797001000105</v>
+        <v>-0.1284334160586892</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
@@ -3069,25 +3069,25 @@
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.01515440308682065</v>
+        <v>0.02206513787728312</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.009579668336211303</v>
+        <v>0.1516287018265908</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.0468107666023125</v>
+        <v>-0.08591236653437558</v>
       </c>
       <c r="DY5" t="n">
         <v>-0</v>
@@ -3096,10 +3096,10 @@
         <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.02921393859205576</v>
+        <v>0.09581917862911232</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.01431956995744334</v>
+        <v>0.04027508529279056</v>
       </c>
       <c r="EC5" t="n">
         <v>0</v>
@@ -3108,25 +3108,25 @@
         <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.03381188172023993</v>
+        <v>-0.03079756122882678</v>
       </c>
       <c r="EH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI5" t="n">
         <v>-0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.01332405059405311</v>
+        <v>-0.03917122253372658</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.03384596103336049</v>
+        <v>0.01229790601816523</v>
       </c>
       <c r="EL5" t="n">
         <v>-0</v>
@@ -3135,13 +3135,13 @@
         <v>-0</v>
       </c>
       <c r="EN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.03358558061923612</v>
+        <v>-0.03997354097047578</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
@@ -3150,13 +3150,13 @@
         <v>-0</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.006699547886820608</v>
+        <v>-0.1123377051953602</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.004051194981766691</v>
+        <v>0.0110379251465177</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
@@ -3168,7 +3168,7 @@
         <v>0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.03691880530666464</v>
+        <v>-0.1624301658955563</v>
       </c>
       <c r="EZ5" t="n">
         <v>-0</v>
@@ -3177,25 +3177,25 @@
         <v>-0</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.007592433114835911</v>
+        <v>0.01077013684796831</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.03584873379244093</v>
+        <v>0.1167006839372136</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
         <v>0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
         <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.02113800646607456</v>
+        <v>0.09835018060599673</v>
       </c>
       <c r="FI5" t="n">
         <v>0</v>
@@ -3204,25 +3204,25 @@
         <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.01264562921169815</v>
+        <v>-0.03603830282378974</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.03154009075545897</v>
+        <v>0.1380126935321841</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
         <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.001738165228662885</v>
+        <v>0.02396480015362012</v>
       </c>
       <c r="FR5" t="n">
         <v>-0</v>
@@ -3231,37 +3231,37 @@
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>-0.02377997533538515</v>
+        <v>-0.05132523783995464</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.02189201655433314</v>
+        <v>-0.02222808092623349</v>
       </c>
       <c r="FV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.005932175969692238</v>
+        <v>-0.03119115905110057</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
         <v>-0</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0.01806336878785947</v>
+        <v>0.14614525878096</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
@@ -3278,46 +3278,46 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2650050552336102</v>
+        <v>0.249027327547678</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.08540261505905275</v>
+        <v>-0.1039970860381959</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.06975935624334557</v>
+        <v>0.005102570623100672</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.02848423300111132</v>
+        <v>-0.1116850877672301</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H6" t="n">
         <v>-0</v>
       </c>
       <c r="I6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2005425909663803</v>
+        <v>0.2992648488818383</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0469943466558634</v>
+        <v>-0.09888741878714856</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.04950597859014896</v>
+        <v>-0.07156062136863897</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.02572641147043984</v>
+        <v>-0.07684771733471335</v>
       </c>
       <c r="P6" t="n">
         <v>-0</v>
@@ -3332,133 +3332,133 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.06693374759666799</v>
+        <v>0.1042140587440149</v>
       </c>
       <c r="U6" t="n">
         <v>-0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.01951193003928579</v>
+        <v>-0.07546360958350587</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0323346273786867</v>
+        <v>-0.09181681117021052</v>
       </c>
       <c r="X6" t="n">
-        <v>0.009331752982247294</v>
+        <v>-0.05424444718777578</v>
       </c>
       <c r="Y6" t="n">
         <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.05170185397648627</v>
+        <v>-0.05733282575330979</v>
       </c>
       <c r="AD6" t="n">
         <v>-0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.01795248072868565</v>
+        <v>-0.1375405768613344</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.007370823556753229</v>
+        <v>-0.02843048848614434</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.01553611506841176</v>
+        <v>0.05376093495995564</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.01749806933138082</v>
+        <v>0.07620863324794441</v>
       </c>
       <c r="AM6" t="n">
         <v>-0</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.05718022179325975</v>
+        <v>-0.07211119139797018</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.05612006660120532</v>
+        <v>0.02997404418316774</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.03241313368255059</v>
+        <v>-0.03724727579007161</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.283709686611043</v>
+        <v>0.3603495274571381</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.03799887563040592</v>
+        <v>-0.1528886722530149</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.03156966548561439</v>
+        <v>-0.2018129319214596</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.03179248766445465</v>
+        <v>-0.166437506254554</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
         <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.03857323132062866</v>
+        <v>-0.0415745301318473</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.06708321841754265</v>
+        <v>-0.07021492633720067</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.1089795276012803</v>
+        <v>0.005112754921982095</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.04732587658507667</v>
+        <v>-0.09785357523193189</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
@@ -3467,52 +3467,52 @@
         <v>-0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.05716311196925</v>
+        <v>0.03624617049247352</v>
       </c>
       <c r="BN6" t="n">
         <v>-0</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.05144928529924453</v>
+        <v>0.07958018939536891</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.0969430017859292</v>
+        <v>0.01349651784040254</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.03554574642186482</v>
+        <v>0.0104093269296282</v>
       </c>
       <c r="BR6" t="n">
         <v>0</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU6" t="n">
         <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.1270514975099279</v>
+        <v>0.1950483753457889</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.0008018622796258022</v>
+        <v>-0.09039625522185822</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.01434587305899816</v>
+        <v>-0.06764743250590358</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.01244655151281326</v>
+        <v>-0.1303099297385667</v>
       </c>
       <c r="CA6" t="n">
         <v>-0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC6" t="n">
         <v>-0</v>
@@ -3521,22 +3521,22 @@
         <v>0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.06739645866687233</v>
+        <v>-0.08965416294631859</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.01058010982736738</v>
+        <v>0.09017318740581234</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.000167696443055077</v>
+        <v>-0.003744394432621063</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.02326035387194274</v>
+        <v>0.04262726363915661</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
@@ -3548,49 +3548,49 @@
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.0004563207409788877</v>
+        <v>-0.02033285749113068</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0.02145531359072898</v>
+        <v>0.08425727299422703</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.02742448701147641</v>
+        <v>0.04645953571720601</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.008938100021586157</v>
+        <v>0.01536426539140878</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.0548676370488267</v>
+        <v>-0.097334941253773</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.03137085279995845</v>
+        <v>0.1100057958453151</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.003399438728241294</v>
+        <v>0.002864686545440955</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.02270225672176187</v>
+        <v>0.07032382080882771</v>
       </c>
       <c r="DB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC6" t="n">
         <v>-0</v>
@@ -3602,19 +3602,19 @@
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.02150088328165945</v>
+        <v>-0.05420950208610163</v>
       </c>
       <c r="DG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.04760994177240586</v>
+        <v>0.023444112619843</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.003956014878707961</v>
+        <v>0.009200420788710457</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.01211590241616265</v>
+        <v>0.02488552882447583</v>
       </c>
       <c r="DK6" t="n">
         <v>-0</v>
@@ -3623,31 +3623,31 @@
         <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.009691239470002538</v>
+        <v>0.0006608814544339273</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.03921305234909025</v>
+        <v>0.01599843077978104</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.01792211719686711</v>
+        <v>-0.1030395015917234</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.02249507212371893</v>
+        <v>-0.008142391488326442</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
       </c>
       <c r="DU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV6" t="n">
         <v>0</v>
@@ -3656,76 +3656,76 @@
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.03283059838521874</v>
+        <v>-0.03421514678468975</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>-0.01638419330862931</v>
+        <v>0.07825713762211674</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.008181814645566087</v>
+        <v>0.005783623328588454</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.03278814517648578</v>
+        <v>-0.03475952361142329</v>
       </c>
       <c r="EC6" t="n">
         <v>0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
         <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.07838729814648575</v>
+        <v>-0.0806831319280388</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.03280448861266706</v>
+        <v>0.09199625827097606</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.05359052649747519</v>
+        <v>0.0193243416531384</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.01666918280884291</v>
+        <v>-0.036272286935615</v>
       </c>
       <c r="EL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM6" t="n">
         <v>-0</v>
       </c>
       <c r="EN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO6" t="n">
         <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.04977002161745193</v>
+        <v>-0.03450502888511527</v>
       </c>
       <c r="EQ6" t="n">
         <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.0247012017739537</v>
+        <v>0.0609551997732563</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.01955589592977269</v>
+        <v>0.01752867232073513</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.0411708205520129</v>
+        <v>0.07581684700087714</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
         <v>0</v>
@@ -3737,19 +3737,19 @@
         <v>0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.0545583148656341</v>
+        <v>-0.1014948293199905</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.01357296279110911</v>
+        <v>0.1283210047609431</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.008851729330875975</v>
+        <v>-0.01515149501166281</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.02804907976287273</v>
+        <v>0.05657620585043636</v>
       </c>
       <c r="FD6" t="n">
         <v>0</v>
@@ -3761,79 +3761,79 @@
         <v>0</v>
       </c>
       <c r="FG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.02425699566946161</v>
+        <v>0.09704186372855188</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.03839659592325681</v>
+        <v>0.08967153372796453</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.001711482106203641</v>
+        <v>0.007460468439977981</v>
       </c>
       <c r="FL6" t="n">
-        <v>-0.01543114945773326</v>
+        <v>0.144217944672616</v>
       </c>
       <c r="FM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO6" t="n">
         <v>0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.0038207607570778</v>
+        <v>0.01292869213476163</v>
       </c>
       <c r="FR6" t="n">
         <v>0</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.0171613403516136</v>
+        <v>0.1511968485040224</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.02240357659577574</v>
+        <v>-0.04224949618086624</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.021148376001634</v>
+        <v>0.004225501040959629</v>
       </c>
       <c r="FV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX6" t="n">
         <v>0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.01759752878040514</v>
+        <v>-0.02898381804717588</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
-        <v>-0.05007373062138434</v>
+        <v>0.03407079336371571</v>
       </c>
       <c r="GC6" t="n">
         <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.02551342436708259</v>
+        <v>0.07627047447481823</v>
       </c>
       <c r="GE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF6" t="n">
         <v>0</v>
@@ -3847,43 +3847,43 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2387077326513741</v>
+        <v>0.2215322855406511</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.06797784265224502</v>
+        <v>-0.08079226242696226</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001104353515527399</v>
+        <v>-0.02016813462993244</v>
       </c>
       <c r="F7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1755553893213557</v>
+        <v>0.2633574869799849</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.06562201846455426</v>
+        <v>-0.0892453523440256</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.01033087717111966</v>
+        <v>-0.05682904430409131</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3901,19 +3901,19 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.06227265993710771</v>
+        <v>0.05709312059146299</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01248100295046824</v>
+        <v>-0.02100990021384219</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07309294609813236</v>
+        <v>-0.0298876619281884</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -3922,112 +3922,112 @@
         <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.06290120153465241</v>
+        <v>-0.0121731531045291</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.01986259900349703</v>
+        <v>-0.09044999853162897</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.01468156550347631</v>
+        <v>-0.01320952748630769</v>
       </c>
       <c r="AG7" t="n">
         <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.01928408265896196</v>
+        <v>0.06948722428070421</v>
       </c>
       <c r="AM7" t="n">
         <v>-0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.06023233303281686</v>
+        <v>-0.05501460077428859</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.04753725293071204</v>
+        <v>0.07577286768521159</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.2358114980705751</v>
+        <v>0.209726271567324</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.0251648680282537</v>
+        <v>-0.05016551727715616</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1222662474380745</v>
+        <v>-0.1217762517991149</v>
       </c>
       <c r="AY7" t="n">
         <v>-0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
         <v>-0</v>
       </c>
       <c r="BC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.03701665347282697</v>
+        <v>-0.0002954124804574009</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.1045919969614737</v>
+        <v>-0.03481541974007678</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.06599275087908038</v>
+        <v>-0.03824798642571543</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.04892852460553179</v>
+        <v>-0.007816482788425914</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.03216264329681798</v>
+        <v>0.02128912590302387</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1603512934418344</v>
+        <v>0.05874445731005184</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
@@ -4057,52 +4057,52 @@
         <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
         <v>0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.100258298234984</v>
+        <v>0.1477717059555307</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.03564841989720731</v>
+        <v>-0.04455999138645179</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0829458903503518</v>
+        <v>-0.02206597306520466</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.06375369148944911</v>
+        <v>-0.08643282900751541</v>
       </c>
       <c r="CF7" t="n">
         <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.002057769314283808</v>
+        <v>0.06991048155246572</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.01211326570539124</v>
+        <v>0.0007775842720287341</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ7" t="n">
         <v>0</v>
@@ -4117,22 +4117,22 @@
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.007045938190649382</v>
+        <v>-0.03656406692152463</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.04091356998396182</v>
+        <v>0.09783575108328708</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.04152978998435907</v>
+        <v>0.0178055101731727</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT7" t="n">
         <v>0</v>
@@ -4144,16 +4144,16 @@
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.04897435773996345</v>
+        <v>-0.08397317352705837</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.01407872682882558</v>
+        <v>0.08032853063722784</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.01055997007038905</v>
+        <v>0.005926514242300427</v>
       </c>
       <c r="DA7" t="n">
         <v>-0</v>
@@ -4171,16 +4171,16 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.03329815417478197</v>
+        <v>-0.04520296707651449</v>
       </c>
       <c r="DG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.01542770324616192</v>
+        <v>0.017640048201015</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.01639791657613373</v>
+        <v>-0.04859064878530735</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
@@ -4192,76 +4192,76 @@
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.03008037215508554</v>
+        <v>-0.03716930061347866</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.05652770668976206</v>
+        <v>-0.07453626424573065</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.02108192290297939</v>
+        <v>-0.04941527942768822</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
       </c>
       <c r="DU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW7" t="n">
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.04520444708774131</v>
+        <v>-0.02180477969716717</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.004664726215604025</v>
+        <v>0.03619524976552568</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.01267861156450676</v>
+        <v>-0.02380579988771007</v>
       </c>
       <c r="EB7" t="n">
         <v>0</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.06565789102703237</v>
+        <v>-0.06136348149235122</v>
       </c>
       <c r="EH7" t="n">
         <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.01726239131675898</v>
+        <v>0.04812467311105083</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.04920354457150818</v>
+        <v>0.03369574305309238</v>
       </c>
       <c r="EK7" t="n">
         <v>0</v>
@@ -4270,55 +4270,55 @@
         <v>-0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
         <v>-0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.04520889281590022</v>
+        <v>-0.02257998965145745</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.01966675362094232</v>
+        <v>-0.001199203358449382</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.03223192967828856</v>
+        <v>-0.00859310801383986</v>
       </c>
       <c r="ET7" t="n">
         <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.05065950007802948</v>
+        <v>-0.09143585770166456</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>-0.009093770341052227</v>
+        <v>0.09278531423937351</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.005435958414426116</v>
+        <v>-0.01538801888340146</v>
       </c>
       <c r="FC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD7" t="n">
         <v>0</v>
@@ -4333,16 +4333,16 @@
         <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.03770416571436889</v>
+        <v>0.08445161908174242</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.0009175467341158154</v>
+        <v>0.06760642479062147</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.03981059378440965</v>
+        <v>-0.01357754812205016</v>
       </c>
       <c r="FL7" t="n">
         <v>-0</v>
@@ -4354,69 +4354,69 @@
         <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.00144458590414132</v>
+        <v>0.00121688941597181</v>
       </c>
       <c r="FR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS7" t="n">
-        <v>-0.001284400071262812</v>
+        <v>0.0929289061692383</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.006469988742281124</v>
+        <v>-0.01806901786159286</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
         <v>0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.01972838523788178</v>
+        <v>-0.06488978468003571</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.09186509288272342</v>
+        <v>0.02264964297637794</v>
       </c>
       <c r="GC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD7" t="n">
         <v>-0</v>
       </c>
       <c r="GE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2878147212338333</v>
+        <v>0.3592665774559661</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -4425,10 +4425,10 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.06903426678540173</v>
+        <v>0.0124110029667905</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1861605570832192</v>
+        <v>-0.3185349832123135</v>
       </c>
       <c r="G8" t="n">
         <v>-0</v>
@@ -4437,13 +4437,13 @@
         <v>-0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2577700144135838</v>
+        <v>0.4887661062873814</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -4452,25 +4452,25 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.01676982683713597</v>
+        <v>-0.06469976493982263</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1812069610603313</v>
+        <v>-0.408413885587264</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02997240260031061</v>
+        <v>0.1348631657901264</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -4479,67 +4479,67 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.01091782248889533</v>
+        <v>-0.08997640117938424</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.01066161805841402</v>
+        <v>-0.0684747771039094</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB8" t="n">
         <v>-0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.01514748725954933</v>
+        <v>-0.02099978615454538</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.03799535978859657</v>
+        <v>-0.2762934213857937</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.004067049017134807</v>
+        <v>0.09734500500817471</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI8" t="n">
         <v>-0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.04255185539692295</v>
+        <v>0.1238131272451377</v>
       </c>
       <c r="AM8" t="n">
         <v>-0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.004216380830539836</v>
+        <v>-0.05949332035183696</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.0639193299035308</v>
+        <v>-0.08840890567862766</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR8" t="n">
         <v>-0</v>
@@ -4548,37 +4548,37 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.2284602772073094</v>
+        <v>0.6463937434838852</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.01842010448539014</v>
+        <v>-0.2885792206392588</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.07901639720775332</v>
+        <v>-0.1997911008837412</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.05833942486599913</v>
+        <v>-0.1126946781311991</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
@@ -4587,64 +4587,64 @@
         <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.06472983427533363</v>
+        <v>-0.02566080516115521</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.08219059373657751</v>
+        <v>-0.03750661578764619</v>
       </c>
       <c r="BI8" t="n">
         <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.04620553626372256</v>
+        <v>0.1267599079000587</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO8" t="n">
         <v>-0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.01785785903410116</v>
+        <v>0.07541834802918621</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.005465321145655151</v>
+        <v>0.04127890339293192</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
         <v>-0</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.114615607703585</v>
+        <v>0.3700263990427802</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX8" t="n">
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.02948840970321008</v>
+        <v>-0.03550810160760057</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.04878079628020656</v>
+        <v>-0.182342771419829</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
@@ -4653,28 +4653,28 @@
         <v>-0</v>
       </c>
       <c r="CC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD8" t="n">
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.0648703088395393</v>
+        <v>-0.1485052524197779</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
         <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.007721770691504358</v>
+        <v>0.03170414698786368</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.03872908045458783</v>
+        <v>0.10798569496285</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
         <v>0</v>
@@ -4686,73 +4686,73 @@
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.003525744495956261</v>
+        <v>-0.1446464043346002</v>
       </c>
       <c r="CO8" t="n">
         <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.01611087152957932</v>
+        <v>0.1146393546140499</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.05644652086419788</v>
+        <v>0.02857141539470635</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV8" t="n">
         <v>-0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.05921382478101779</v>
+        <v>-0.1404595684646018</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
         <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.007590635846527114</v>
+        <v>0.01524570695447108</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.0401456629436726</v>
+        <v>0.1398991042049428</v>
       </c>
       <c r="DB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC8" t="n">
         <v>-0</v>
       </c>
       <c r="DD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.03323712693232195</v>
+        <v>-0.1112803389875733</v>
       </c>
       <c r="DG8" t="n">
         <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.06211845463833868</v>
+        <v>-0.05844885863992825</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.04859796409482577</v>
+        <v>0.08664942347776897</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
@@ -4761,13 +4761,13 @@
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
         <v>-0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.02722390994583234</v>
+        <v>-0.08910546458876216</v>
       </c>
       <c r="DP8" t="n">
         <v>0</v>
@@ -4776,94 +4776,94 @@
         <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.02287095351202065</v>
+        <v>-0.0005639195766592671</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.01431597885538048</v>
+        <v>0.1093306977228302</v>
       </c>
       <c r="DT8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW8" t="n">
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>-0.05460411774411725</v>
+        <v>-0.06335993665451449</v>
       </c>
       <c r="DY8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.01521494923011018</v>
+        <v>-0.007427109329146578</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.03231451210163941</v>
+        <v>0.0352411578116134</v>
       </c>
       <c r="EC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF8" t="n">
         <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.06896587327047683</v>
+        <v>-0.03320885329837635</v>
       </c>
       <c r="EH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI8" t="n">
         <v>-0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.02754018855389256</v>
+        <v>-0.02386518241475493</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.0253394665324788</v>
+        <v>0.02759106305415946</v>
       </c>
       <c r="EL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM8" t="n">
         <v>-0</v>
       </c>
       <c r="EN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO8" t="n">
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.05035544475187786</v>
+        <v>-0.05758744597421768</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
         <v>-0</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.03500058140180162</v>
+        <v>-0.07571519355732911</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.008463769422931347</v>
+        <v>-0.008201805572983724</v>
       </c>
       <c r="EU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
@@ -4875,46 +4875,46 @@
         <v>0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.05914737327037439</v>
+        <v>-0.1689420317745762</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA8" t="n">
         <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0.001121468935411549</v>
+        <v>-0.006821154732513475</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.03988739638894542</v>
+        <v>0.1216136351736869</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
         <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
         <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.03157828800321573</v>
+        <v>0.113972084665418</v>
       </c>
       <c r="FI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ8" t="n">
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.007263258386767567</v>
+        <v>-0.06401186692973805</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.03666540696353879</v>
+        <v>0.1740780511956319</v>
       </c>
       <c r="FM8" t="n">
         <v>0</v>
@@ -4926,10 +4926,10 @@
         <v>0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.000422044898886936</v>
+        <v>0.009837011797909613</v>
       </c>
       <c r="FR8" t="n">
         <v>-0</v>
@@ -4938,37 +4938,37 @@
         <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>-0.002354695548638968</v>
+        <v>-0.007780681991905951</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.04851509601175726</v>
+        <v>-0.0723317750183132</v>
       </c>
       <c r="FV8" t="n">
         <v>-0</v>
       </c>
       <c r="FW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.0005669519955003551</v>
+        <v>-0.02381991724614782</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
         <v>-0</v>
       </c>
       <c r="GC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.04211418995605395</v>
+        <v>0.1680208705088072</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
@@ -4977,7 +4977,7 @@
         <v>-0</v>
       </c>
       <c r="GG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4985,7 +4985,7 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4870340664615532</v>
+        <v>0.3451182324101872</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -4994,16 +4994,16 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1171038079518017</v>
+        <v>-0.02415007276200525</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4436249964418046</v>
+        <v>-0.1423975481477552</v>
       </c>
       <c r="G9" t="n">
         <v>-0</v>
       </c>
       <c r="H9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4564442769178869</v>
+        <v>0.4556398729406052</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -5021,25 +5021,25 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.05570592675916219</v>
+        <v>-0.1057542333602102</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4518573142021146</v>
+        <v>-0.2037387679502438</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03678668043720053</v>
+        <v>0.0994621737550056</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -5048,16 +5048,16 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.08439262822239568</v>
+        <v>-0.1181451646230026</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.01567068857811676</v>
+        <v>-0.01165391202914747</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -5066,19 +5066,19 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.02363507836424826</v>
+        <v>-0.03181093238320283</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.01012467495818293</v>
+        <v>-0.2802260515972894</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.03447034086699631</v>
+        <v>-0.0004806981102348303</v>
       </c>
       <c r="AH9" t="n">
         <v>-0</v>
@@ -5093,7 +5093,7 @@
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.08346482370634739</v>
+        <v>0.03391320067782991</v>
       </c>
       <c r="AM9" t="n">
         <v>-0</v>
@@ -5102,10 +5102,10 @@
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.001425139274130004</v>
+        <v>-0.04382687751844315</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.08288815890890448</v>
+        <v>0.01800998439388342</v>
       </c>
       <c r="AQ9" t="n">
         <v>-0</v>
@@ -5117,10 +5117,10 @@
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.4142823062989933</v>
+        <v>0.490930550772916</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
@@ -5129,16 +5129,16 @@
         <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.07056162875261536</v>
+        <v>-0.2412630341333792</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.2195072107427806</v>
+        <v>-0.1060183635823349</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
         <v>0</v>
@@ -5147,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.1084983479853896</v>
+        <v>-0.03244371999040717</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
@@ -5156,52 +5156,52 @@
         <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.1511296373082835</v>
+        <v>-0.01743696709524062</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0.1920463743209763</v>
+        <v>-0.08854328880803962</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.1430673738132707</v>
+        <v>0.0555858806580355</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO9" t="n">
         <v>-0</v>
       </c>
       <c r="BP9" t="n">
-        <v>-0.003506804419984493</v>
+        <v>0.08095184223925117</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.01774829638850664</v>
+        <v>-0.0353695774531211</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU9" t="n">
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.2174578064331273</v>
+        <v>0.2645884054932645</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.07027843473932166</v>
+        <v>-0.07607225122038919</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0.1317131469424722</v>
+        <v>-0.1065766498934343</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
@@ -5228,22 +5228,22 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.08493679991571336</v>
+        <v>-0.1128628071677499</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
         <v>-0</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.005132296706541574</v>
+        <v>0.02940671068759908</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.107260316561954</v>
+        <v>0.05005876308788209</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
@@ -5255,100 +5255,100 @@
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.411111576022698e-05</v>
+        <v>-0.1176648399683078</v>
       </c>
       <c r="CO9" t="n">
         <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.01656313510158922</v>
+        <v>0.0987659328249483</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0.02173635870421967</v>
+        <v>0.09696302121904032</v>
       </c>
       <c r="CS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.06794519309467903</v>
+        <v>-0.1132667735478171</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
         <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.002517826506811512</v>
+        <v>0.008266387471978583</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.1129463761574095</v>
+        <v>0.07134993351079165</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
         <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.04002326517017469</v>
+        <v>-0.04182103570936625</v>
       </c>
       <c r="DG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.0444566794875837</v>
+        <v>-0.1773522024170269</v>
       </c>
       <c r="DJ9" t="n">
-        <v>-0.001614683906987056</v>
+        <v>0.05430905562071246</v>
       </c>
       <c r="DK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM9" t="n">
         <v>0</v>
       </c>
       <c r="DN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.006081052987154392</v>
+        <v>-0.006789881564130029</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.03351720870604942</v>
+        <v>-0.06165173203514228</v>
       </c>
       <c r="DS9" t="n">
-        <v>-0.00651404814989466</v>
+        <v>0.07945600496514979</v>
       </c>
       <c r="DT9" t="n">
         <v>-0</v>
@@ -5357,13 +5357,13 @@
         <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW9" t="n">
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.05777594466092893</v>
+        <v>-0.0203989119697206</v>
       </c>
       <c r="DY9" t="n">
         <v>0</v>
@@ -5372,106 +5372,106 @@
         <v>-0</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.01639577769065341</v>
+        <v>-0.0676568575607339</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.05440360332127209</v>
+        <v>0.03633715307927934</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
         <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.09693440032671177</v>
+        <v>-0.04598912915854268</v>
       </c>
       <c r="EH9" t="n">
         <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.02439302318152298</v>
+        <v>0.02204225341916105</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.1195640580710318</v>
+        <v>-0.009853383573066175</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
         <v>-0</v>
       </c>
       <c r="EN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.02990216264525762</v>
+        <v>-0.005227696832770167</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER9" t="n">
         <v>-0</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.01296633880913288</v>
+        <v>-0.01220162516658875</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.07094629067274934</v>
+        <v>0.1364584260180013</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
       </c>
       <c r="EW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.06543195927951648</v>
+        <v>-0.130932432158351</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA9" t="n">
         <v>-0</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.006229404879093165</v>
+        <v>-0.002061555924192711</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.1024537790435004</v>
+        <v>0.03987951912620769</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
         <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.002535719417640378</v>
+        <v>0.2075057372435904</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
@@ -5480,16 +5480,16 @@
         <v>-0</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.008508884200727705</v>
+        <v>-0.08888362194263089</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.05172385674770193</v>
+        <v>0.1169911234280748</v>
       </c>
       <c r="FM9" t="n">
         <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
         <v>0</v>
@@ -5498,46 +5498,46 @@
         <v>0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.004963051982165477</v>
+        <v>0.01095474566180105</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
         <v>-0</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.008810654514323803</v>
+        <v>-0.02433236845990461</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.03438754936987051</v>
+        <v>-0.04959525460895942</v>
       </c>
       <c r="FV9" t="n">
         <v>-0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.04462418624405818</v>
+        <v>-0.0392241248176862</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0.05108333755087999</v>
+        <v>0.06229019800014492</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
@@ -5546,7 +5546,7 @@
         <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -6692,7 +6692,7 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1555227955103367</v>
+        <v>0.3740873085411197</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -6701,25 +6701,25 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.08280241633837762</v>
+        <v>-0.01212069175337799</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.07228254118439849</v>
+        <v>-0.1420221622722794</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1280013609926359</v>
+        <v>0.4550155857997566</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -6728,25 +6728,25 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.05768573777505789</v>
+        <v>-0.1030346101625517</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.07598714090533507</v>
+        <v>-0.1872297503630286</v>
       </c>
       <c r="P12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.01378244307605709</v>
+        <v>0.08850790259557874</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -6755,40 +6755,40 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.004451178988662641</v>
+        <v>-0.08737791763617689</v>
       </c>
       <c r="X12" t="n">
-        <v>0.009296517155136153</v>
+        <v>-0.01195679459117023</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.004937052603166965</v>
+        <v>-0.03445648712941773</v>
       </c>
       <c r="AD12" t="n">
         <v>-0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.01397086337945391</v>
+        <v>-0.2456376296061947</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.01246458326384953</v>
+        <v>0.01208147322881906</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
@@ -6800,22 +6800,22 @@
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.01048426267962558</v>
+        <v>0.03864887039576933</v>
       </c>
       <c r="AM12" t="n">
         <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.008843058167262783</v>
+        <v>-0.03478953138166604</v>
       </c>
       <c r="AP12" t="n">
-        <v>-0.01472490147678882</v>
+        <v>0.004348853773135694</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR12" t="n">
         <v>-0</v>
@@ -6824,28 +6824,28 @@
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.1072825700670186</v>
+        <v>0.4082565567656767</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.02880010261672456</v>
+        <v>-0.2569226983256364</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0.02119212093019258</v>
+        <v>-0.1019174011449789</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>0</v>
@@ -6854,7 +6854,7 @@
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.03149636970574076</v>
+        <v>-0.007966828915457077</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
@@ -6863,52 +6863,52 @@
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.05775229627875221</v>
+        <v>0.003299825105484479</v>
       </c>
       <c r="BH12" t="n">
-        <v>-0.05909104473704765</v>
+        <v>-0.06672767056896817</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.03556435611813727</v>
+        <v>0.03790515352353375</v>
       </c>
       <c r="BN12" t="n">
         <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.0160377211932141</v>
+        <v>0.05412149956945281</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.01704690532514525</v>
+        <v>-0.02904912448350688</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
       </c>
       <c r="BT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.05103091105067987</v>
+        <v>0.2284431608214726</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
@@ -6917,10 +6917,10 @@
         <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>-0.01218046926464564</v>
+        <v>-0.06484531704446789</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0.01384008897907786</v>
+        <v>-0.108101791999787</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
@@ -6929,31 +6929,31 @@
         <v>-0</v>
       </c>
       <c r="CC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.02622308846222178</v>
+        <v>-0.106248834828522</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
         <v>-0</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.007127736093176795</v>
+        <v>0.02637823890535754</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.01772200217820961</v>
+        <v>0.05235108424751526</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL12" t="n">
         <v>0</v>
@@ -6962,52 +6962,52 @@
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.0008607606247808709</v>
+        <v>-0.1167963372686887</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.007075855757484145</v>
+        <v>0.1418910920064637</v>
       </c>
       <c r="CR12" t="n">
-        <v>-0.01179765717120735</v>
+        <v>0.06948314519810558</v>
       </c>
       <c r="CS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
         <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.01997228527183853</v>
+        <v>-0.1042914444843911</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.006098553888960175</v>
+        <v>0.01336787605902164</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.01817422480022265</v>
+        <v>0.07393732256271993</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD12" t="n">
         <v>0</v>
@@ -7016,22 +7016,22 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.03236358042313904</v>
+        <v>-0.07613463879940778</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.05139714038333401</v>
+        <v>-0.2088158290936235</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.01369322867674388</v>
+        <v>0.0664830782668345</v>
       </c>
       <c r="DK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL12" t="n">
         <v>-0</v>
@@ -7040,28 +7040,28 @@
         <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.005787316285419271</v>
+        <v>-0.01453139399809695</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
         <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.01937102480609069</v>
+        <v>-0.04380413370108927</v>
       </c>
       <c r="DS12" t="n">
-        <v>-0.009748317299426336</v>
+        <v>0.04598420032442908</v>
       </c>
       <c r="DT12" t="n">
         <v>-0</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
         <v>-0</v>
@@ -7070,49 +7070,49 @@
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.02951577427682513</v>
+        <v>-0.008128724834928856</v>
       </c>
       <c r="DY12" t="n">
         <v>0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.01498315768491325</v>
+        <v>-0.05739258479727879</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.01825960522851271</v>
+        <v>0.02186635189298738</v>
       </c>
       <c r="EC12" t="n">
         <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.0315053328593496</v>
+        <v>-0.04910027289638845</v>
       </c>
       <c r="EH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.00944317674849344</v>
+        <v>0.009966225733988959</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.01334605781814872</v>
+        <v>-0.0008290111176221996</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
         <v>-0</v>
@@ -7121,82 +7121,82 @@
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.01243019102766987</v>
+        <v>-0.03263751016830274</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
         <v>-0</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.002243096035829807</v>
+        <v>-0.01666909488296208</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0.01165242559899074</v>
+        <v>0.1081606505080878</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
       </c>
       <c r="EW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.0208915055260241</v>
+        <v>-0.1236182570442468</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.009264301360075101</v>
+        <v>0.001119420975175839</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.02170654796978215</v>
+        <v>0.04480882699908054</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>-0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
         <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.01511337365004362</v>
+        <v>0.1682489665630392</v>
       </c>
       <c r="FI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ12" t="n">
         <v>-0</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.0113268961668335</v>
+        <v>-0.08182097191585727</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.01985781488408164</v>
+        <v>0.1168730928665216</v>
       </c>
       <c r="FM12" t="n">
         <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO12" t="n">
         <v>0</v>
@@ -7205,63 +7205,63 @@
         <v>0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>7.644719732458803e-05</v>
+        <v>0.001766033095943371</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
         <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.001509859052916248</v>
+        <v>-0.008890543018079875</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.01880918805336776</v>
+        <v>-0.02826654740530361</v>
       </c>
       <c r="FV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.001820653164314721</v>
+        <v>-0.03526500023485375</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
         <v>-0</v>
       </c>
       <c r="GC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0.005457780234660795</v>
+        <v>0.06675703004937075</v>
       </c>
       <c r="GE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF12" t="n">
         <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.1266462604957166</v>
+        <v>0.2568294364946774</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -7270,10 +7270,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0359596502453245</v>
+        <v>0.08360029537802897</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1458807809284861</v>
+        <v>-0.1124021230301778</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -7282,10 +7282,10 @@
         <v>-0</v>
       </c>
       <c r="I13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1005695273084039</v>
+        <v>0.2217196001047798</v>
       </c>
       <c r="K13" t="n">
         <v>-0</v>
@@ -7294,43 +7294,43 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.002737779122467324</v>
+        <v>-0.007165351043765546</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0997243053547566</v>
+        <v>-0.1079803910484537</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>-0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01760666690443216</v>
+        <v>-0.06928175277144705</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.03898100455986269</v>
+        <v>-0.04621480493013201</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.02367567826519899</v>
+        <v>-0.08056909819103956</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -7339,7 +7339,7 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.01516222809156062</v>
+        <v>0.0545615304003013</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -7348,43 +7348,43 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.02746700724001907</v>
+        <v>-0.03953367418522752</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.02875747820365326</v>
+        <v>0.05219803461472458</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.02170311454758471</v>
+        <v>0.01635961694893267</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.007094937415410008</v>
+        <v>0.0310684134670413</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.01299687962429524</v>
+        <v>0.01725490832228489</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -7393,25 +7393,25 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.08472652476482592</v>
+        <v>-0.0180578642833223</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.1007914678233191</v>
+        <v>0.08887558904301493</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.08600565149370705</v>
+        <v>-0.007113253437926324</v>
       </c>
       <c r="AZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
         <v>0</v>
@@ -7420,22 +7420,22 @@
         <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.01499549256361632</v>
+        <v>0.1617831854512066</v>
       </c>
       <c r="BD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.01190784752073141</v>
+        <v>-0.02019540684000256</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.04702454220862393</v>
+        <v>0.002295561210419389</v>
       </c>
       <c r="BI13" t="n">
         <v>0</v>
@@ -7447,10 +7447,10 @@
         <v>-0</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.007487808577764449</v>
+        <v>-0.06679451029213296</v>
       </c>
       <c r="BM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN13" t="n">
         <v>-0</v>
@@ -7459,37 +7459,37 @@
         <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.003610416424803363</v>
+        <v>-0.1113391538630767</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.008104688305153049</v>
+        <v>0.03653506681344443</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>0</v>
       </c>
       <c r="BT13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.03643594286452657</v>
+        <v>-0.02642080760106553</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
       </c>
       <c r="BW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.03598242985426318</v>
+        <v>-0.0702652693062062</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.06421245250715174</v>
+        <v>-0.1104025499013803</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
@@ -7498,10 +7498,10 @@
         <v>0</v>
       </c>
       <c r="CC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>-0.02249073403637856</v>
+        <v>-0.06422544393623388</v>
       </c>
       <c r="CE13" t="n">
         <v>0</v>
@@ -7513,13 +7513,13 @@
         <v>0</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.01066464430794283</v>
+        <v>0.007021126430780321</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.04343561869056956</v>
+        <v>0.03115380220022167</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
@@ -7528,25 +7528,25 @@
         <v>-0</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.004126862283695319</v>
+        <v>0.01181028276288585</v>
       </c>
       <c r="CN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.06820944344543946</v>
+        <v>0.08373939567032432</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.001346799260798693</v>
+        <v>-0.04380478783386278</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
         <v>-0</v>
@@ -7555,7 +7555,7 @@
         <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>-0.02108001772460196</v>
+        <v>-0.06726026660128644</v>
       </c>
       <c r="CW13" t="n">
         <v>-0</v>
@@ -7567,40 +7567,40 @@
         <v>-0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.01460815439289092</v>
+        <v>0.004563328884568592</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.03937246904179714</v>
+        <v>0.03598994833441783</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
         <v>-0</v>
       </c>
       <c r="DD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE13" t="n">
-        <v>-0.0001534932277220459</v>
+        <v>-0.005146031250466448</v>
       </c>
       <c r="DF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG13" t="n">
         <v>-0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.03079357996395915</v>
+        <v>-0.06032322361351384</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.001550474019576347</v>
+        <v>0.01431398112090277</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
         <v>0</v>
@@ -7609,7 +7609,7 @@
         <v>0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0.0005372762060466832</v>
+        <v>-0.03987372890085466</v>
       </c>
       <c r="DO13" t="n">
         <v>0</v>
@@ -7618,13 +7618,13 @@
         <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.03730876190525402</v>
+        <v>-0.05332094162376333</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.01723860783134225</v>
+        <v>0.08169112504517606</v>
       </c>
       <c r="DT13" t="n">
         <v>-0</v>
@@ -7633,37 +7633,37 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW13" t="n">
-        <v>-0.008746059748456648</v>
+        <v>0.02465871043844876</v>
       </c>
       <c r="DX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY13" t="n">
         <v>-0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.01650795672862657</v>
+        <v>0.1237911810008313</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.03860945368572078</v>
+        <v>0.06352424167544639</v>
       </c>
       <c r="EC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE13" t="n">
         <v>0</v>
       </c>
       <c r="EF13" t="n">
-        <v>-0.02203262574153988</v>
+        <v>0.003466002153019663</v>
       </c>
       <c r="EG13" t="n">
         <v>0</v>
@@ -7675,22 +7675,22 @@
         <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>-0.003408451035381646</v>
+        <v>-0.02625681375732344</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.04728923408716374</v>
+        <v>0.0510532135942809</v>
       </c>
       <c r="EL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN13" t="n">
         <v>0</v>
       </c>
       <c r="EO13" t="n">
-        <v>-0.01277627041603102</v>
+        <v>-0.03844273207820576</v>
       </c>
       <c r="EP13" t="n">
         <v>0</v>
@@ -7699,13 +7699,13 @@
         <v>-0</v>
       </c>
       <c r="ER13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.02803751493072065</v>
+        <v>0.006067814825159359</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.002817743768328517</v>
+        <v>0.04406886628997701</v>
       </c>
       <c r="EU13" t="n">
         <v>0</v>
@@ -7717,7 +7717,7 @@
         <v>-0</v>
       </c>
       <c r="EX13" t="n">
-        <v>-0.01808398236400945</v>
+        <v>-0.05967497713790787</v>
       </c>
       <c r="EY13" t="n">
         <v>0</v>
@@ -7729,22 +7729,22 @@
         <v>0</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.02408577528846209</v>
+        <v>-0.006747037493913817</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.04115578127544132</v>
+        <v>0.04533085295682484</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.007376195651755181</v>
+        <v>0.127769368547643</v>
       </c>
       <c r="FH13" t="n">
         <v>-0</v>
@@ -7753,13 +7753,13 @@
         <v>0</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.01202097803954294</v>
+        <v>-5.861337664423544e-05</v>
       </c>
       <c r="FL13" t="n">
-        <v>-0.002121784118489793</v>
+        <v>0.1059281336776556</v>
       </c>
       <c r="FM13" t="n">
         <v>0</v>
@@ -7771,10 +7771,10 @@
         <v>-0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.0006546982649096399</v>
+        <v>0.003074093359563177</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR13" t="n">
         <v>-0</v>
@@ -7783,13 +7783,13 @@
         <v>0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.0006216824476783274</v>
+        <v>0.001590208613466223</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.01139849522618542</v>
+        <v>0.04096364891334509</v>
       </c>
       <c r="FV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW13" t="n">
         <v>-0</v>
@@ -7798,28 +7798,28 @@
         <v>0</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.00460258118434362</v>
+        <v>0.0725763631748053</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA13" t="n">
         <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.01054367872908787</v>
+        <v>0.07896609230274053</v>
       </c>
       <c r="GE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG13" t="n">
         <v>0</v>
